--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_05-08-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_05-08-2025.xlsx
@@ -591,25 +591,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60f7de415+77285]
-	GetHandleVerifier [0x0x7ff60f7de470+77376]
-	(No symbol) [0x0x7ff60f5a9a6a]
-	(No symbol) [0x0x7ff60f600406]
-	(No symbol) [0x0x7ff60f6006bc]
-	(No symbol) [0x0x7ff60f653ac7]
-	(No symbol) [0x0x7ff60f62864f]
-	(No symbol) [0x0x7ff60f65087f]
-	(No symbol) [0x0x7ff60f6283e3]
-	(No symbol) [0x0x7ff60f5f1521]
-	(No symbol) [0x0x7ff60f5f22b3]
-	GetHandleVerifier [0x0x7ff60fac1efd+3107021]
-	GetHandleVerifier [0x0x7ff60fabc29d+3083373]
-	GetHandleVerifier [0x0x7ff60fadbedd+3213485]
-	GetHandleVerifier [0x0x7ff60f7f884e+184862]
-	GetHandleVerifier [0x0x7ff60f80055f+216879]
-	GetHandleVerifier [0x0x7ff60f7e7084+113236]
-	GetHandleVerifier [0x0x7ff60f7e7239+113673]
-	GetHandleVerifier [0x0x7ff60f7ce298+11368]
+	GetHandleVerifier [0x0x7ff6f54ae415+77285]
+	GetHandleVerifier [0x0x7ff6f54ae470+77376]
+	(No symbol) [0x0x7ff6f5279a6a]
+	(No symbol) [0x0x7ff6f52d0406]
+	(No symbol) [0x0x7ff6f52d06bc]
+	(No symbol) [0x0x7ff6f5323ac7]
+	(No symbol) [0x0x7ff6f52f864f]
+	(No symbol) [0x0x7ff6f532087f]
+	(No symbol) [0x0x7ff6f52f83e3]
+	(No symbol) [0x0x7ff6f52c1521]
+	(No symbol) [0x0x7ff6f52c22b3]
+	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
+	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
+	GetHandleVerifier [0x0x7ff6f54c884e+184862]
+	GetHandleVerifier [0x0x7ff6f54d055f+216879]
+	GetHandleVerifier [0x0x7ff6f54b7084+113236]
+	GetHandleVerifier [0x0x7ff6f54b7239+113673]
+	GetHandleVerifier [0x0x7ff6f549e298+11368]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -712,25 +712,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60f7de415+77285]
-	GetHandleVerifier [0x0x7ff60f7de470+77376]
-	(No symbol) [0x0x7ff60f5a9a6a]
-	(No symbol) [0x0x7ff60f600406]
-	(No symbol) [0x0x7ff60f6006bc]
-	(No symbol) [0x0x7ff60f653ac7]
-	(No symbol) [0x0x7ff60f62864f]
-	(No symbol) [0x0x7ff60f65087f]
-	(No symbol) [0x0x7ff60f6283e3]
-	(No symbol) [0x0x7ff60f5f1521]
-	(No symbol) [0x0x7ff60f5f22b3]
-	GetHandleVerifier [0x0x7ff60fac1efd+3107021]
-	GetHandleVerifier [0x0x7ff60fabc29d+3083373]
-	GetHandleVerifier [0x0x7ff60fadbedd+3213485]
-	GetHandleVerifier [0x0x7ff60f7f884e+184862]
-	GetHandleVerifier [0x0x7ff60f80055f+216879]
-	GetHandleVerifier [0x0x7ff60f7e7084+113236]
-	GetHandleVerifier [0x0x7ff60f7e7239+113673]
-	GetHandleVerifier [0x0x7ff60f7ce298+11368]
+	GetHandleVerifier [0x0x7ff6f54ae415+77285]
+	GetHandleVerifier [0x0x7ff6f54ae470+77376]
+	(No symbol) [0x0x7ff6f5279a6a]
+	(No symbol) [0x0x7ff6f52d0406]
+	(No symbol) [0x0x7ff6f52d06bc]
+	(No symbol) [0x0x7ff6f5323ac7]
+	(No symbol) [0x0x7ff6f52f864f]
+	(No symbol) [0x0x7ff6f532087f]
+	(No symbol) [0x0x7ff6f52f83e3]
+	(No symbol) [0x0x7ff6f52c1521]
+	(No symbol) [0x0x7ff6f52c22b3]
+	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
+	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
+	GetHandleVerifier [0x0x7ff6f54c884e+184862]
+	GetHandleVerifier [0x0x7ff6f54d055f+216879]
+	GetHandleVerifier [0x0x7ff6f54b7084+113236]
+	GetHandleVerifier [0x0x7ff6f54b7239+113673]
+	GetHandleVerifier [0x0x7ff6f549e298+11368]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -833,25 +833,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60f7de415+77285]
-	GetHandleVerifier [0x0x7ff60f7de470+77376]
-	(No symbol) [0x0x7ff60f5a9a6a]
-	(No symbol) [0x0x7ff60f600406]
-	(No symbol) [0x0x7ff60f6006bc]
-	(No symbol) [0x0x7ff60f653ac7]
-	(No symbol) [0x0x7ff60f62864f]
-	(No symbol) [0x0x7ff60f65087f]
-	(No symbol) [0x0x7ff60f6283e3]
-	(No symbol) [0x0x7ff60f5f1521]
-	(No symbol) [0x0x7ff60f5f22b3]
-	GetHandleVerifier [0x0x7ff60fac1efd+3107021]
-	GetHandleVerifier [0x0x7ff60fabc29d+3083373]
-	GetHandleVerifier [0x0x7ff60fadbedd+3213485]
-	GetHandleVerifier [0x0x7ff60f7f884e+184862]
-	GetHandleVerifier [0x0x7ff60f80055f+216879]
-	GetHandleVerifier [0x0x7ff60f7e7084+113236]
-	GetHandleVerifier [0x0x7ff60f7e7239+113673]
-	GetHandleVerifier [0x0x7ff60f7ce298+11368]
+	GetHandleVerifier [0x0x7ff6f54ae415+77285]
+	GetHandleVerifier [0x0x7ff6f54ae470+77376]
+	(No symbol) [0x0x7ff6f5279a6a]
+	(No symbol) [0x0x7ff6f52d0406]
+	(No symbol) [0x0x7ff6f52d06bc]
+	(No symbol) [0x0x7ff6f5323ac7]
+	(No symbol) [0x0x7ff6f52f864f]
+	(No symbol) [0x0x7ff6f532087f]
+	(No symbol) [0x0x7ff6f52f83e3]
+	(No symbol) [0x0x7ff6f52c1521]
+	(No symbol) [0x0x7ff6f52c22b3]
+	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
+	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
+	GetHandleVerifier [0x0x7ff6f54c884e+184862]
+	GetHandleVerifier [0x0x7ff6f54d055f+216879]
+	GetHandleVerifier [0x0x7ff6f54b7084+113236]
+	GetHandleVerifier [0x0x7ff6f54b7239+113673]
+	GetHandleVerifier [0x0x7ff6f549e298+11368]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -954,25 +954,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60f7de415+77285]
-	GetHandleVerifier [0x0x7ff60f7de470+77376]
-	(No symbol) [0x0x7ff60f5a9a6a]
-	(No symbol) [0x0x7ff60f600406]
-	(No symbol) [0x0x7ff60f6006bc]
-	(No symbol) [0x0x7ff60f653ac7]
-	(No symbol) [0x0x7ff60f62864f]
-	(No symbol) [0x0x7ff60f65087f]
-	(No symbol) [0x0x7ff60f6283e3]
-	(No symbol) [0x0x7ff60f5f1521]
-	(No symbol) [0x0x7ff60f5f22b3]
-	GetHandleVerifier [0x0x7ff60fac1efd+3107021]
-	GetHandleVerifier [0x0x7ff60fabc29d+3083373]
-	GetHandleVerifier [0x0x7ff60fadbedd+3213485]
-	GetHandleVerifier [0x0x7ff60f7f884e+184862]
-	GetHandleVerifier [0x0x7ff60f80055f+216879]
-	GetHandleVerifier [0x0x7ff60f7e7084+113236]
-	GetHandleVerifier [0x0x7ff60f7e7239+113673]
-	GetHandleVerifier [0x0x7ff60f7ce298+11368]
+	GetHandleVerifier [0x0x7ff6f54ae415+77285]
+	GetHandleVerifier [0x0x7ff6f54ae470+77376]
+	(No symbol) [0x0x7ff6f5279a6a]
+	(No symbol) [0x0x7ff6f52d0406]
+	(No symbol) [0x0x7ff6f52d06bc]
+	(No symbol) [0x0x7ff6f5323ac7]
+	(No symbol) [0x0x7ff6f52f864f]
+	(No symbol) [0x0x7ff6f532087f]
+	(No symbol) [0x0x7ff6f52f83e3]
+	(No symbol) [0x0x7ff6f52c1521]
+	(No symbol) [0x0x7ff6f52c22b3]
+	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
+	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
+	GetHandleVerifier [0x0x7ff6f54c884e+184862]
+	GetHandleVerifier [0x0x7ff6f54d055f+216879]
+	GetHandleVerifier [0x0x7ff6f54b7084+113236]
+	GetHandleVerifier [0x0x7ff6f54b7239+113673]
+	GetHandleVerifier [0x0x7ff6f549e298+11368]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1075,25 +1075,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60f7de415+77285]
-	GetHandleVerifier [0x0x7ff60f7de470+77376]
-	(No symbol) [0x0x7ff60f5a9a6a]
-	(No symbol) [0x0x7ff60f600406]
-	(No symbol) [0x0x7ff60f6006bc]
-	(No symbol) [0x0x7ff60f653ac7]
-	(No symbol) [0x0x7ff60f62864f]
-	(No symbol) [0x0x7ff60f65087f]
-	(No symbol) [0x0x7ff60f6283e3]
-	(No symbol) [0x0x7ff60f5f1521]
-	(No symbol) [0x0x7ff60f5f22b3]
-	GetHandleVerifier [0x0x7ff60fac1efd+3107021]
-	GetHandleVerifier [0x0x7ff60fabc29d+3083373]
-	GetHandleVerifier [0x0x7ff60fadbedd+3213485]
-	GetHandleVerifier [0x0x7ff60f7f884e+184862]
-	GetHandleVerifier [0x0x7ff60f80055f+216879]
-	GetHandleVerifier [0x0x7ff60f7e7084+113236]
-	GetHandleVerifier [0x0x7ff60f7e7239+113673]
-	GetHandleVerifier [0x0x7ff60f7ce298+11368]
+	GetHandleVerifier [0x0x7ff6f54ae415+77285]
+	GetHandleVerifier [0x0x7ff6f54ae470+77376]
+	(No symbol) [0x0x7ff6f5279a6a]
+	(No symbol) [0x0x7ff6f52d0406]
+	(No symbol) [0x0x7ff6f52d06bc]
+	(No symbol) [0x0x7ff6f5323ac7]
+	(No symbol) [0x0x7ff6f52f864f]
+	(No symbol) [0x0x7ff6f532087f]
+	(No symbol) [0x0x7ff6f52f83e3]
+	(No symbol) [0x0x7ff6f52c1521]
+	(No symbol) [0x0x7ff6f52c22b3]
+	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
+	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
+	GetHandleVerifier [0x0x7ff6f54c884e+184862]
+	GetHandleVerifier [0x0x7ff6f54d055f+216879]
+	GetHandleVerifier [0x0x7ff6f54b7084+113236]
+	GetHandleVerifier [0x0x7ff6f54b7239+113673]
+	GetHandleVerifier [0x0x7ff6f549e298+11368]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1196,25 +1196,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60f7de415+77285]
-	GetHandleVerifier [0x0x7ff60f7de470+77376]
-	(No symbol) [0x0x7ff60f5a9a6a]
-	(No symbol) [0x0x7ff60f600406]
-	(No symbol) [0x0x7ff60f6006bc]
-	(No symbol) [0x0x7ff60f653ac7]
-	(No symbol) [0x0x7ff60f62864f]
-	(No symbol) [0x0x7ff60f65087f]
-	(No symbol) [0x0x7ff60f6283e3]
-	(No symbol) [0x0x7ff60f5f1521]
-	(No symbol) [0x0x7ff60f5f22b3]
-	GetHandleVerifier [0x0x7ff60fac1efd+3107021]
-	GetHandleVerifier [0x0x7ff60fabc29d+3083373]
-	GetHandleVerifier [0x0x7ff60fadbedd+3213485]
-	GetHandleVerifier [0x0x7ff60f7f884e+184862]
-	GetHandleVerifier [0x0x7ff60f80055f+216879]
-	GetHandleVerifier [0x0x7ff60f7e7084+113236]
-	GetHandleVerifier [0x0x7ff60f7e7239+113673]
-	GetHandleVerifier [0x0x7ff60f7ce298+11368]
+	GetHandleVerifier [0x0x7ff6f54ae415+77285]
+	GetHandleVerifier [0x0x7ff6f54ae470+77376]
+	(No symbol) [0x0x7ff6f5279a6a]
+	(No symbol) [0x0x7ff6f52d0406]
+	(No symbol) [0x0x7ff6f52d06bc]
+	(No symbol) [0x0x7ff6f5323ac7]
+	(No symbol) [0x0x7ff6f52f864f]
+	(No symbol) [0x0x7ff6f532087f]
+	(No symbol) [0x0x7ff6f52f83e3]
+	(No symbol) [0x0x7ff6f52c1521]
+	(No symbol) [0x0x7ff6f52c22b3]
+	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
+	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
+	GetHandleVerifier [0x0x7ff6f54c884e+184862]
+	GetHandleVerifier [0x0x7ff6f54d055f+216879]
+	GetHandleVerifier [0x0x7ff6f54b7084+113236]
+	GetHandleVerifier [0x0x7ff6f54b7239+113673]
+	GetHandleVerifier [0x0x7ff6f549e298+11368]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1317,25 +1317,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60f7de415+77285]
-	GetHandleVerifier [0x0x7ff60f7de470+77376]
-	(No symbol) [0x0x7ff60f5a9a6a]
-	(No symbol) [0x0x7ff60f600406]
-	(No symbol) [0x0x7ff60f6006bc]
-	(No symbol) [0x0x7ff60f653ac7]
-	(No symbol) [0x0x7ff60f62864f]
-	(No symbol) [0x0x7ff60f65087f]
-	(No symbol) [0x0x7ff60f6283e3]
-	(No symbol) [0x0x7ff60f5f1521]
-	(No symbol) [0x0x7ff60f5f22b3]
-	GetHandleVerifier [0x0x7ff60fac1efd+3107021]
-	GetHandleVerifier [0x0x7ff60fabc29d+3083373]
-	GetHandleVerifier [0x0x7ff60fadbedd+3213485]
-	GetHandleVerifier [0x0x7ff60f7f884e+184862]
-	GetHandleVerifier [0x0x7ff60f80055f+216879]
-	GetHandleVerifier [0x0x7ff60f7e7084+113236]
-	GetHandleVerifier [0x0x7ff60f7e7239+113673]
-	GetHandleVerifier [0x0x7ff60f7ce298+11368]
+	GetHandleVerifier [0x0x7ff6f54ae415+77285]
+	GetHandleVerifier [0x0x7ff6f54ae470+77376]
+	(No symbol) [0x0x7ff6f5279a6a]
+	(No symbol) [0x0x7ff6f52d0406]
+	(No symbol) [0x0x7ff6f52d06bc]
+	(No symbol) [0x0x7ff6f5323ac7]
+	(No symbol) [0x0x7ff6f52f864f]
+	(No symbol) [0x0x7ff6f532087f]
+	(No symbol) [0x0x7ff6f52f83e3]
+	(No symbol) [0x0x7ff6f52c1521]
+	(No symbol) [0x0x7ff6f52c22b3]
+	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
+	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
+	GetHandleVerifier [0x0x7ff6f54c884e+184862]
+	GetHandleVerifier [0x0x7ff6f54d055f+216879]
+	GetHandleVerifier [0x0x7ff6f54b7084+113236]
+	GetHandleVerifier [0x0x7ff6f54b7239+113673]
+	GetHandleVerifier [0x0x7ff6f549e298+11368]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1438,25 +1438,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60f7de415+77285]
-	GetHandleVerifier [0x0x7ff60f7de470+77376]
-	(No symbol) [0x0x7ff60f5a9a6a]
-	(No symbol) [0x0x7ff60f600406]
-	(No symbol) [0x0x7ff60f6006bc]
-	(No symbol) [0x0x7ff60f653ac7]
-	(No symbol) [0x0x7ff60f62864f]
-	(No symbol) [0x0x7ff60f65087f]
-	(No symbol) [0x0x7ff60f6283e3]
-	(No symbol) [0x0x7ff60f5f1521]
-	(No symbol) [0x0x7ff60f5f22b3]
-	GetHandleVerifier [0x0x7ff60fac1efd+3107021]
-	GetHandleVerifier [0x0x7ff60fabc29d+3083373]
-	GetHandleVerifier [0x0x7ff60fadbedd+3213485]
-	GetHandleVerifier [0x0x7ff60f7f884e+184862]
-	GetHandleVerifier [0x0x7ff60f80055f+216879]
-	GetHandleVerifier [0x0x7ff60f7e7084+113236]
-	GetHandleVerifier [0x0x7ff60f7e7239+113673]
-	GetHandleVerifier [0x0x7ff60f7ce298+11368]
+	GetHandleVerifier [0x0x7ff6f54ae415+77285]
+	GetHandleVerifier [0x0x7ff6f54ae470+77376]
+	(No symbol) [0x0x7ff6f5279a6a]
+	(No symbol) [0x0x7ff6f52d0406]
+	(No symbol) [0x0x7ff6f52d06bc]
+	(No symbol) [0x0x7ff6f5323ac7]
+	(No symbol) [0x0x7ff6f52f864f]
+	(No symbol) [0x0x7ff6f532087f]
+	(No symbol) [0x0x7ff6f52f83e3]
+	(No symbol) [0x0x7ff6f52c1521]
+	(No symbol) [0x0x7ff6f52c22b3]
+	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
+	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
+	GetHandleVerifier [0x0x7ff6f54c884e+184862]
+	GetHandleVerifier [0x0x7ff6f54d055f+216879]
+	GetHandleVerifier [0x0x7ff6f54b7084+113236]
+	GetHandleVerifier [0x0x7ff6f54b7239+113673]
+	GetHandleVerifier [0x0x7ff6f549e298+11368]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1559,25 +1559,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60f7de415+77285]
-	GetHandleVerifier [0x0x7ff60f7de470+77376]
-	(No symbol) [0x0x7ff60f5a9a6a]
-	(No symbol) [0x0x7ff60f600406]
-	(No symbol) [0x0x7ff60f6006bc]
-	(No symbol) [0x0x7ff60f653ac7]
-	(No symbol) [0x0x7ff60f62864f]
-	(No symbol) [0x0x7ff60f65087f]
-	(No symbol) [0x0x7ff60f6283e3]
-	(No symbol) [0x0x7ff60f5f1521]
-	(No symbol) [0x0x7ff60f5f22b3]
-	GetHandleVerifier [0x0x7ff60fac1efd+3107021]
-	GetHandleVerifier [0x0x7ff60fabc29d+3083373]
-	GetHandleVerifier [0x0x7ff60fadbedd+3213485]
-	GetHandleVerifier [0x0x7ff60f7f884e+184862]
-	GetHandleVerifier [0x0x7ff60f80055f+216879]
-	GetHandleVerifier [0x0x7ff60f7e7084+113236]
-	GetHandleVerifier [0x0x7ff60f7e7239+113673]
-	GetHandleVerifier [0x0x7ff60f7ce298+11368]
+	GetHandleVerifier [0x0x7ff6f54ae415+77285]
+	GetHandleVerifier [0x0x7ff6f54ae470+77376]
+	(No symbol) [0x0x7ff6f5279a6a]
+	(No symbol) [0x0x7ff6f52d0406]
+	(No symbol) [0x0x7ff6f52d06bc]
+	(No symbol) [0x0x7ff6f5323ac7]
+	(No symbol) [0x0x7ff6f52f864f]
+	(No symbol) [0x0x7ff6f532087f]
+	(No symbol) [0x0x7ff6f52f83e3]
+	(No symbol) [0x0x7ff6f52c1521]
+	(No symbol) [0x0x7ff6f52c22b3]
+	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
+	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
+	GetHandleVerifier [0x0x7ff6f54c884e+184862]
+	GetHandleVerifier [0x0x7ff6f54d055f+216879]
+	GetHandleVerifier [0x0x7ff6f54b7084+113236]
+	GetHandleVerifier [0x0x7ff6f54b7239+113673]
+	GetHandleVerifier [0x0x7ff6f549e298+11368]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1680,25 +1680,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60f7de415+77285]
-	GetHandleVerifier [0x0x7ff60f7de470+77376]
-	(No symbol) [0x0x7ff60f5a9a6a]
-	(No symbol) [0x0x7ff60f600406]
-	(No symbol) [0x0x7ff60f6006bc]
-	(No symbol) [0x0x7ff60f653ac7]
-	(No symbol) [0x0x7ff60f62864f]
-	(No symbol) [0x0x7ff60f65087f]
-	(No symbol) [0x0x7ff60f6283e3]
-	(No symbol) [0x0x7ff60f5f1521]
-	(No symbol) [0x0x7ff60f5f22b3]
-	GetHandleVerifier [0x0x7ff60fac1efd+3107021]
-	GetHandleVerifier [0x0x7ff60fabc29d+3083373]
-	GetHandleVerifier [0x0x7ff60fadbedd+3213485]
-	GetHandleVerifier [0x0x7ff60f7f884e+184862]
-	GetHandleVerifier [0x0x7ff60f80055f+216879]
-	GetHandleVerifier [0x0x7ff60f7e7084+113236]
-	GetHandleVerifier [0x0x7ff60f7e7239+113673]
-	GetHandleVerifier [0x0x7ff60f7ce298+11368]
+	GetHandleVerifier [0x0x7ff6f54ae415+77285]
+	GetHandleVerifier [0x0x7ff6f54ae470+77376]
+	(No symbol) [0x0x7ff6f5279a6a]
+	(No symbol) [0x0x7ff6f52d0406]
+	(No symbol) [0x0x7ff6f52d06bc]
+	(No symbol) [0x0x7ff6f5323ac7]
+	(No symbol) [0x0x7ff6f52f864f]
+	(No symbol) [0x0x7ff6f532087f]
+	(No symbol) [0x0x7ff6f52f83e3]
+	(No symbol) [0x0x7ff6f52c1521]
+	(No symbol) [0x0x7ff6f52c22b3]
+	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
+	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
+	GetHandleVerifier [0x0x7ff6f54c884e+184862]
+	GetHandleVerifier [0x0x7ff6f54d055f+216879]
+	GetHandleVerifier [0x0x7ff6f54b7084+113236]
+	GetHandleVerifier [0x0x7ff6f54b7239+113673]
+	GetHandleVerifier [0x0x7ff6f549e298+11368]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1801,25 +1801,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60f7de415+77285]
-	GetHandleVerifier [0x0x7ff60f7de470+77376]
-	(No symbol) [0x0x7ff60f5a9a6a]
-	(No symbol) [0x0x7ff60f600406]
-	(No symbol) [0x0x7ff60f6006bc]
-	(No symbol) [0x0x7ff60f653ac7]
-	(No symbol) [0x0x7ff60f62864f]
-	(No symbol) [0x0x7ff60f65087f]
-	(No symbol) [0x0x7ff60f6283e3]
-	(No symbol) [0x0x7ff60f5f1521]
-	(No symbol) [0x0x7ff60f5f22b3]
-	GetHandleVerifier [0x0x7ff60fac1efd+3107021]
-	GetHandleVerifier [0x0x7ff60fabc29d+3083373]
-	GetHandleVerifier [0x0x7ff60fadbedd+3213485]
-	GetHandleVerifier [0x0x7ff60f7f884e+184862]
-	GetHandleVerifier [0x0x7ff60f80055f+216879]
-	GetHandleVerifier [0x0x7ff60f7e7084+113236]
-	GetHandleVerifier [0x0x7ff60f7e7239+113673]
-	GetHandleVerifier [0x0x7ff60f7ce298+11368]
+	GetHandleVerifier [0x0x7ff6f54ae415+77285]
+	GetHandleVerifier [0x0x7ff6f54ae470+77376]
+	(No symbol) [0x0x7ff6f5279a6a]
+	(No symbol) [0x0x7ff6f52d0406]
+	(No symbol) [0x0x7ff6f52d06bc]
+	(No symbol) [0x0x7ff6f5323ac7]
+	(No symbol) [0x0x7ff6f52f864f]
+	(No symbol) [0x0x7ff6f532087f]
+	(No symbol) [0x0x7ff6f52f83e3]
+	(No symbol) [0x0x7ff6f52c1521]
+	(No symbol) [0x0x7ff6f52c22b3]
+	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
+	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
+	GetHandleVerifier [0x0x7ff6f54c884e+184862]
+	GetHandleVerifier [0x0x7ff6f54d055f+216879]
+	GetHandleVerifier [0x0x7ff6f54b7084+113236]
+	GetHandleVerifier [0x0x7ff6f54b7239+113673]
+	GetHandleVerifier [0x0x7ff6f549e298+11368]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1922,25 +1922,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60f7de415+77285]
-	GetHandleVerifier [0x0x7ff60f7de470+77376]
-	(No symbol) [0x0x7ff60f5a9a6a]
-	(No symbol) [0x0x7ff60f600406]
-	(No symbol) [0x0x7ff60f6006bc]
-	(No symbol) [0x0x7ff60f653ac7]
-	(No symbol) [0x0x7ff60f62864f]
-	(No symbol) [0x0x7ff60f65087f]
-	(No symbol) [0x0x7ff60f6283e3]
-	(No symbol) [0x0x7ff60f5f1521]
-	(No symbol) [0x0x7ff60f5f22b3]
-	GetHandleVerifier [0x0x7ff60fac1efd+3107021]
-	GetHandleVerifier [0x0x7ff60fabc29d+3083373]
-	GetHandleVerifier [0x0x7ff60fadbedd+3213485]
-	GetHandleVerifier [0x0x7ff60f7f884e+184862]
-	GetHandleVerifier [0x0x7ff60f80055f+216879]
-	GetHandleVerifier [0x0x7ff60f7e7084+113236]
-	GetHandleVerifier [0x0x7ff60f7e7239+113673]
-	GetHandleVerifier [0x0x7ff60f7ce298+11368]
+	GetHandleVerifier [0x0x7ff6f54ae415+77285]
+	GetHandleVerifier [0x0x7ff6f54ae470+77376]
+	(No symbol) [0x0x7ff6f5279a6a]
+	(No symbol) [0x0x7ff6f52d0406]
+	(No symbol) [0x0x7ff6f52d06bc]
+	(No symbol) [0x0x7ff6f5323ac7]
+	(No symbol) [0x0x7ff6f52f864f]
+	(No symbol) [0x0x7ff6f532087f]
+	(No symbol) [0x0x7ff6f52f83e3]
+	(No symbol) [0x0x7ff6f52c1521]
+	(No symbol) [0x0x7ff6f52c22b3]
+	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
+	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
+	GetHandleVerifier [0x0x7ff6f54c884e+184862]
+	GetHandleVerifier [0x0x7ff6f54d055f+216879]
+	GetHandleVerifier [0x0x7ff6f54b7084+113236]
+	GetHandleVerifier [0x0x7ff6f54b7239+113673]
+	GetHandleVerifier [0x0x7ff6f549e298+11368]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2043,25 +2043,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60f7de415+77285]
-	GetHandleVerifier [0x0x7ff60f7de470+77376]
-	(No symbol) [0x0x7ff60f5a9a6a]
-	(No symbol) [0x0x7ff60f600406]
-	(No symbol) [0x0x7ff60f6006bc]
-	(No symbol) [0x0x7ff60f653ac7]
-	(No symbol) [0x0x7ff60f62864f]
-	(No symbol) [0x0x7ff60f65087f]
-	(No symbol) [0x0x7ff60f6283e3]
-	(No symbol) [0x0x7ff60f5f1521]
-	(No symbol) [0x0x7ff60f5f22b3]
-	GetHandleVerifier [0x0x7ff60fac1efd+3107021]
-	GetHandleVerifier [0x0x7ff60fabc29d+3083373]
-	GetHandleVerifier [0x0x7ff60fadbedd+3213485]
-	GetHandleVerifier [0x0x7ff60f7f884e+184862]
-	GetHandleVerifier [0x0x7ff60f80055f+216879]
-	GetHandleVerifier [0x0x7ff60f7e7084+113236]
-	GetHandleVerifier [0x0x7ff60f7e7239+113673]
-	GetHandleVerifier [0x0x7ff60f7ce298+11368]
+	GetHandleVerifier [0x0x7ff6f54ae415+77285]
+	GetHandleVerifier [0x0x7ff6f54ae470+77376]
+	(No symbol) [0x0x7ff6f5279a6a]
+	(No symbol) [0x0x7ff6f52d0406]
+	(No symbol) [0x0x7ff6f52d06bc]
+	(No symbol) [0x0x7ff6f5323ac7]
+	(No symbol) [0x0x7ff6f52f864f]
+	(No symbol) [0x0x7ff6f532087f]
+	(No symbol) [0x0x7ff6f52f83e3]
+	(No symbol) [0x0x7ff6f52c1521]
+	(No symbol) [0x0x7ff6f52c22b3]
+	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
+	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
+	GetHandleVerifier [0x0x7ff6f54c884e+184862]
+	GetHandleVerifier [0x0x7ff6f54d055f+216879]
+	GetHandleVerifier [0x0x7ff6f54b7084+113236]
+	GetHandleVerifier [0x0x7ff6f54b7239+113673]
+	GetHandleVerifier [0x0x7ff6f549e298+11368]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2164,25 +2164,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60f7de415+77285]
-	GetHandleVerifier [0x0x7ff60f7de470+77376]
-	(No symbol) [0x0x7ff60f5a9a6a]
-	(No symbol) [0x0x7ff60f600406]
-	(No symbol) [0x0x7ff60f6006bc]
-	(No symbol) [0x0x7ff60f653ac7]
-	(No symbol) [0x0x7ff60f62864f]
-	(No symbol) [0x0x7ff60f65087f]
-	(No symbol) [0x0x7ff60f6283e3]
-	(No symbol) [0x0x7ff60f5f1521]
-	(No symbol) [0x0x7ff60f5f22b3]
-	GetHandleVerifier [0x0x7ff60fac1efd+3107021]
-	GetHandleVerifier [0x0x7ff60fabc29d+3083373]
-	GetHandleVerifier [0x0x7ff60fadbedd+3213485]
-	GetHandleVerifier [0x0x7ff60f7f884e+184862]
-	GetHandleVerifier [0x0x7ff60f80055f+216879]
-	GetHandleVerifier [0x0x7ff60f7e7084+113236]
-	GetHandleVerifier [0x0x7ff60f7e7239+113673]
-	GetHandleVerifier [0x0x7ff60f7ce298+11368]
+	GetHandleVerifier [0x0x7ff6f54ae415+77285]
+	GetHandleVerifier [0x0x7ff6f54ae470+77376]
+	(No symbol) [0x0x7ff6f5279a6a]
+	(No symbol) [0x0x7ff6f52d0406]
+	(No symbol) [0x0x7ff6f52d06bc]
+	(No symbol) [0x0x7ff6f5323ac7]
+	(No symbol) [0x0x7ff6f52f864f]
+	(No symbol) [0x0x7ff6f532087f]
+	(No symbol) [0x0x7ff6f52f83e3]
+	(No symbol) [0x0x7ff6f52c1521]
+	(No symbol) [0x0x7ff6f52c22b3]
+	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
+	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
+	GetHandleVerifier [0x0x7ff6f54c884e+184862]
+	GetHandleVerifier [0x0x7ff6f54d055f+216879]
+	GetHandleVerifier [0x0x7ff6f54b7084+113236]
+	GetHandleVerifier [0x0x7ff6f54b7239+113673]
+	GetHandleVerifier [0x0x7ff6f549e298+11368]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2285,25 +2285,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60f7de415+77285]
-	GetHandleVerifier [0x0x7ff60f7de470+77376]
-	(No symbol) [0x0x7ff60f5a9a6a]
-	(No symbol) [0x0x7ff60f600406]
-	(No symbol) [0x0x7ff60f6006bc]
-	(No symbol) [0x0x7ff60f653ac7]
-	(No symbol) [0x0x7ff60f62864f]
-	(No symbol) [0x0x7ff60f65087f]
-	(No symbol) [0x0x7ff60f6283e3]
-	(No symbol) [0x0x7ff60f5f1521]
-	(No symbol) [0x0x7ff60f5f22b3]
-	GetHandleVerifier [0x0x7ff60fac1efd+3107021]
-	GetHandleVerifier [0x0x7ff60fabc29d+3083373]
-	GetHandleVerifier [0x0x7ff60fadbedd+3213485]
-	GetHandleVerifier [0x0x7ff60f7f884e+184862]
-	GetHandleVerifier [0x0x7ff60f80055f+216879]
-	GetHandleVerifier [0x0x7ff60f7e7084+113236]
-	GetHandleVerifier [0x0x7ff60f7e7239+113673]
-	GetHandleVerifier [0x0x7ff60f7ce298+11368]
+	GetHandleVerifier [0x0x7ff6f54ae415+77285]
+	GetHandleVerifier [0x0x7ff6f54ae470+77376]
+	(No symbol) [0x0x7ff6f5279a6a]
+	(No symbol) [0x0x7ff6f52d0406]
+	(No symbol) [0x0x7ff6f52d06bc]
+	(No symbol) [0x0x7ff6f5323ac7]
+	(No symbol) [0x0x7ff6f52f864f]
+	(No symbol) [0x0x7ff6f532087f]
+	(No symbol) [0x0x7ff6f52f83e3]
+	(No symbol) [0x0x7ff6f52c1521]
+	(No symbol) [0x0x7ff6f52c22b3]
+	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
+	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
+	GetHandleVerifier [0x0x7ff6f54c884e+184862]
+	GetHandleVerifier [0x0x7ff6f54d055f+216879]
+	GetHandleVerifier [0x0x7ff6f54b7084+113236]
+	GetHandleVerifier [0x0x7ff6f54b7239+113673]
+	GetHandleVerifier [0x0x7ff6f549e298+11368]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2503,25 +2503,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60f7de415+77285]
-	GetHandleVerifier [0x0x7ff60f7de470+77376]
-	(No symbol) [0x0x7ff60f5a9a6a]
-	(No symbol) [0x0x7ff60f600406]
-	(No symbol) [0x0x7ff60f6006bc]
-	(No symbol) [0x0x7ff60f653ac7]
-	(No symbol) [0x0x7ff60f62864f]
-	(No symbol) [0x0x7ff60f65087f]
-	(No symbol) [0x0x7ff60f6283e3]
-	(No symbol) [0x0x7ff60f5f1521]
-	(No symbol) [0x0x7ff60f5f22b3]
-	GetHandleVerifier [0x0x7ff60fac1efd+3107021]
-	GetHandleVerifier [0x0x7ff60fabc29d+3083373]
-	GetHandleVerifier [0x0x7ff60fadbedd+3213485]
-	GetHandleVerifier [0x0x7ff60f7f884e+184862]
-	GetHandleVerifier [0x0x7ff60f80055f+216879]
-	GetHandleVerifier [0x0x7ff60f7e7084+113236]
-	GetHandleVerifier [0x0x7ff60f7e7239+113673]
-	GetHandleVerifier [0x0x7ff60f7ce298+11368]
+	GetHandleVerifier [0x0x7ff6f54ae415+77285]
+	GetHandleVerifier [0x0x7ff6f54ae470+77376]
+	(No symbol) [0x0x7ff6f5279a6a]
+	(No symbol) [0x0x7ff6f52d0406]
+	(No symbol) [0x0x7ff6f52d06bc]
+	(No symbol) [0x0x7ff6f5323ac7]
+	(No symbol) [0x0x7ff6f52f864f]
+	(No symbol) [0x0x7ff6f532087f]
+	(No symbol) [0x0x7ff6f52f83e3]
+	(No symbol) [0x0x7ff6f52c1521]
+	(No symbol) [0x0x7ff6f52c22b3]
+	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
+	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
+	GetHandleVerifier [0x0x7ff6f54c884e+184862]
+	GetHandleVerifier [0x0x7ff6f54d055f+216879]
+	GetHandleVerifier [0x0x7ff6f54b7084+113236]
+	GetHandleVerifier [0x0x7ff6f54b7239+113673]
+	GetHandleVerifier [0x0x7ff6f549e298+11368]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2624,25 +2624,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60f7de415+77285]
-	GetHandleVerifier [0x0x7ff60f7de470+77376]
-	(No symbol) [0x0x7ff60f5a9a6a]
-	(No symbol) [0x0x7ff60f600406]
-	(No symbol) [0x0x7ff60f6006bc]
-	(No symbol) [0x0x7ff60f653ac7]
-	(No symbol) [0x0x7ff60f62864f]
-	(No symbol) [0x0x7ff60f65087f]
-	(No symbol) [0x0x7ff60f6283e3]
-	(No symbol) [0x0x7ff60f5f1521]
-	(No symbol) [0x0x7ff60f5f22b3]
-	GetHandleVerifier [0x0x7ff60fac1efd+3107021]
-	GetHandleVerifier [0x0x7ff60fabc29d+3083373]
-	GetHandleVerifier [0x0x7ff60fadbedd+3213485]
-	GetHandleVerifier [0x0x7ff60f7f884e+184862]
-	GetHandleVerifier [0x0x7ff60f80055f+216879]
-	GetHandleVerifier [0x0x7ff60f7e7084+113236]
-	GetHandleVerifier [0x0x7ff60f7e7239+113673]
-	GetHandleVerifier [0x0x7ff60f7ce298+11368]
+	GetHandleVerifier [0x0x7ff6f54ae415+77285]
+	GetHandleVerifier [0x0x7ff6f54ae470+77376]
+	(No symbol) [0x0x7ff6f5279a6a]
+	(No symbol) [0x0x7ff6f52d0406]
+	(No symbol) [0x0x7ff6f52d06bc]
+	(No symbol) [0x0x7ff6f5323ac7]
+	(No symbol) [0x0x7ff6f52f864f]
+	(No symbol) [0x0x7ff6f532087f]
+	(No symbol) [0x0x7ff6f52f83e3]
+	(No symbol) [0x0x7ff6f52c1521]
+	(No symbol) [0x0x7ff6f52c22b3]
+	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
+	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
+	GetHandleVerifier [0x0x7ff6f54c884e+184862]
+	GetHandleVerifier [0x0x7ff6f54d055f+216879]
+	GetHandleVerifier [0x0x7ff6f54b7084+113236]
+	GetHandleVerifier [0x0x7ff6f54b7239+113673]
+	GetHandleVerifier [0x0x7ff6f549e298+11368]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2745,25 +2745,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60f7de415+77285]
-	GetHandleVerifier [0x0x7ff60f7de470+77376]
-	(No symbol) [0x0x7ff60f5a9a6a]
-	(No symbol) [0x0x7ff60f600406]
-	(No symbol) [0x0x7ff60f6006bc]
-	(No symbol) [0x0x7ff60f653ac7]
-	(No symbol) [0x0x7ff60f62864f]
-	(No symbol) [0x0x7ff60f65087f]
-	(No symbol) [0x0x7ff60f6283e3]
-	(No symbol) [0x0x7ff60f5f1521]
-	(No symbol) [0x0x7ff60f5f22b3]
-	GetHandleVerifier [0x0x7ff60fac1efd+3107021]
-	GetHandleVerifier [0x0x7ff60fabc29d+3083373]
-	GetHandleVerifier [0x0x7ff60fadbedd+3213485]
-	GetHandleVerifier [0x0x7ff60f7f884e+184862]
-	GetHandleVerifier [0x0x7ff60f80055f+216879]
-	GetHandleVerifier [0x0x7ff60f7e7084+113236]
-	GetHandleVerifier [0x0x7ff60f7e7239+113673]
-	GetHandleVerifier [0x0x7ff60f7ce298+11368]
+	GetHandleVerifier [0x0x7ff6f54ae415+77285]
+	GetHandleVerifier [0x0x7ff6f54ae470+77376]
+	(No symbol) [0x0x7ff6f5279a6a]
+	(No symbol) [0x0x7ff6f52d0406]
+	(No symbol) [0x0x7ff6f52d06bc]
+	(No symbol) [0x0x7ff6f5323ac7]
+	(No symbol) [0x0x7ff6f52f864f]
+	(No symbol) [0x0x7ff6f532087f]
+	(No symbol) [0x0x7ff6f52f83e3]
+	(No symbol) [0x0x7ff6f52c1521]
+	(No symbol) [0x0x7ff6f52c22b3]
+	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
+	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
+	GetHandleVerifier [0x0x7ff6f54c884e+184862]
+	GetHandleVerifier [0x0x7ff6f54d055f+216879]
+	GetHandleVerifier [0x0x7ff6f54b7084+113236]
+	GetHandleVerifier [0x0x7ff6f54b7239+113673]
+	GetHandleVerifier [0x0x7ff6f549e298+11368]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2866,25 +2866,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60f7de415+77285]
-	GetHandleVerifier [0x0x7ff60f7de470+77376]
-	(No symbol) [0x0x7ff60f5a9a6a]
-	(No symbol) [0x0x7ff60f600406]
-	(No symbol) [0x0x7ff60f6006bc]
-	(No symbol) [0x0x7ff60f653ac7]
-	(No symbol) [0x0x7ff60f62864f]
-	(No symbol) [0x0x7ff60f65087f]
-	(No symbol) [0x0x7ff60f6283e3]
-	(No symbol) [0x0x7ff60f5f1521]
-	(No symbol) [0x0x7ff60f5f22b3]
-	GetHandleVerifier [0x0x7ff60fac1efd+3107021]
-	GetHandleVerifier [0x0x7ff60fabc29d+3083373]
-	GetHandleVerifier [0x0x7ff60fadbedd+3213485]
-	GetHandleVerifier [0x0x7ff60f7f884e+184862]
-	GetHandleVerifier [0x0x7ff60f80055f+216879]
-	GetHandleVerifier [0x0x7ff60f7e7084+113236]
-	GetHandleVerifier [0x0x7ff60f7e7239+113673]
-	GetHandleVerifier [0x0x7ff60f7ce298+11368]
+	GetHandleVerifier [0x0x7ff6f54ae415+77285]
+	GetHandleVerifier [0x0x7ff6f54ae470+77376]
+	(No symbol) [0x0x7ff6f5279a6a]
+	(No symbol) [0x0x7ff6f52d0406]
+	(No symbol) [0x0x7ff6f52d06bc]
+	(No symbol) [0x0x7ff6f5323ac7]
+	(No symbol) [0x0x7ff6f52f864f]
+	(No symbol) [0x0x7ff6f532087f]
+	(No symbol) [0x0x7ff6f52f83e3]
+	(No symbol) [0x0x7ff6f52c1521]
+	(No symbol) [0x0x7ff6f52c22b3]
+	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
+	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
+	GetHandleVerifier [0x0x7ff6f54c884e+184862]
+	GetHandleVerifier [0x0x7ff6f54d055f+216879]
+	GetHandleVerifier [0x0x7ff6f54b7084+113236]
+	GetHandleVerifier [0x0x7ff6f54b7239+113673]
+	GetHandleVerifier [0x0x7ff6f549e298+11368]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2987,25 +2987,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60f7de415+77285]
-	GetHandleVerifier [0x0x7ff60f7de470+77376]
-	(No symbol) [0x0x7ff60f5a9a6a]
-	(No symbol) [0x0x7ff60f600406]
-	(No symbol) [0x0x7ff60f6006bc]
-	(No symbol) [0x0x7ff60f653ac7]
-	(No symbol) [0x0x7ff60f62864f]
-	(No symbol) [0x0x7ff60f65087f]
-	(No symbol) [0x0x7ff60f6283e3]
-	(No symbol) [0x0x7ff60f5f1521]
-	(No symbol) [0x0x7ff60f5f22b3]
-	GetHandleVerifier [0x0x7ff60fac1efd+3107021]
-	GetHandleVerifier [0x0x7ff60fabc29d+3083373]
-	GetHandleVerifier [0x0x7ff60fadbedd+3213485]
-	GetHandleVerifier [0x0x7ff60f7f884e+184862]
-	GetHandleVerifier [0x0x7ff60f80055f+216879]
-	GetHandleVerifier [0x0x7ff60f7e7084+113236]
-	GetHandleVerifier [0x0x7ff60f7e7239+113673]
-	GetHandleVerifier [0x0x7ff60f7ce298+11368]
+	GetHandleVerifier [0x0x7ff6f54ae415+77285]
+	GetHandleVerifier [0x0x7ff6f54ae470+77376]
+	(No symbol) [0x0x7ff6f5279a6a]
+	(No symbol) [0x0x7ff6f52d0406]
+	(No symbol) [0x0x7ff6f52d06bc]
+	(No symbol) [0x0x7ff6f5323ac7]
+	(No symbol) [0x0x7ff6f52f864f]
+	(No symbol) [0x0x7ff6f532087f]
+	(No symbol) [0x0x7ff6f52f83e3]
+	(No symbol) [0x0x7ff6f52c1521]
+	(No symbol) [0x0x7ff6f52c22b3]
+	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
+	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
+	GetHandleVerifier [0x0x7ff6f54c884e+184862]
+	GetHandleVerifier [0x0x7ff6f54d055f+216879]
+	GetHandleVerifier [0x0x7ff6f54b7084+113236]
+	GetHandleVerifier [0x0x7ff6f54b7239+113673]
+	GetHandleVerifier [0x0x7ff6f549e298+11368]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -3108,25 +3108,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60f7de415+77285]
-	GetHandleVerifier [0x0x7ff60f7de470+77376]
-	(No symbol) [0x0x7ff60f5a9a6a]
-	(No symbol) [0x0x7ff60f600406]
-	(No symbol) [0x0x7ff60f6006bc]
-	(No symbol) [0x0x7ff60f653ac7]
-	(No symbol) [0x0x7ff60f62864f]
-	(No symbol) [0x0x7ff60f65087f]
-	(No symbol) [0x0x7ff60f6283e3]
-	(No symbol) [0x0x7ff60f5f1521]
-	(No symbol) [0x0x7ff60f5f22b3]
-	GetHandleVerifier [0x0x7ff60fac1efd+3107021]
-	GetHandleVerifier [0x0x7ff60fabc29d+3083373]
-	GetHandleVerifier [0x0x7ff60fadbedd+3213485]
-	GetHandleVerifier [0x0x7ff60f7f884e+184862]
-	GetHandleVerifier [0x0x7ff60f80055f+216879]
-	GetHandleVerifier [0x0x7ff60f7e7084+113236]
-	GetHandleVerifier [0x0x7ff60f7e7239+113673]
-	GetHandleVerifier [0x0x7ff60f7ce298+11368]
+	GetHandleVerifier [0x0x7ff6f54ae415+77285]
+	GetHandleVerifier [0x0x7ff6f54ae470+77376]
+	(No symbol) [0x0x7ff6f5279a6a]
+	(No symbol) [0x0x7ff6f52d0406]
+	(No symbol) [0x0x7ff6f52d06bc]
+	(No symbol) [0x0x7ff6f5323ac7]
+	(No symbol) [0x0x7ff6f52f864f]
+	(No symbol) [0x0x7ff6f532087f]
+	(No symbol) [0x0x7ff6f52f83e3]
+	(No symbol) [0x0x7ff6f52c1521]
+	(No symbol) [0x0x7ff6f52c22b3]
+	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
+	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
+	GetHandleVerifier [0x0x7ff6f54c884e+184862]
+	GetHandleVerifier [0x0x7ff6f54d055f+216879]
+	GetHandleVerifier [0x0x7ff6f54b7084+113236]
+	GetHandleVerifier [0x0x7ff6f54b7239+113673]
+	GetHandleVerifier [0x0x7ff6f549e298+11368]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -3229,25 +3229,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60f7de415+77285]
-	GetHandleVerifier [0x0x7ff60f7de470+77376]
-	(No symbol) [0x0x7ff60f5a9a6a]
-	(No symbol) [0x0x7ff60f600406]
-	(No symbol) [0x0x7ff60f6006bc]
-	(No symbol) [0x0x7ff60f653ac7]
-	(No symbol) [0x0x7ff60f62864f]
-	(No symbol) [0x0x7ff60f65087f]
-	(No symbol) [0x0x7ff60f6283e3]
-	(No symbol) [0x0x7ff60f5f1521]
-	(No symbol) [0x0x7ff60f5f22b3]
-	GetHandleVerifier [0x0x7ff60fac1efd+3107021]
-	GetHandleVerifier [0x0x7ff60fabc29d+3083373]
-	GetHandleVerifier [0x0x7ff60fadbedd+3213485]
-	GetHandleVerifier [0x0x7ff60f7f884e+184862]
-	GetHandleVerifier [0x0x7ff60f80055f+216879]
-	GetHandleVerifier [0x0x7ff60f7e7084+113236]
-	GetHandleVerifier [0x0x7ff60f7e7239+113673]
-	GetHandleVerifier [0x0x7ff60f7ce298+11368]
+	GetHandleVerifier [0x0x7ff6f54ae415+77285]
+	GetHandleVerifier [0x0x7ff6f54ae470+77376]
+	(No symbol) [0x0x7ff6f5279a6a]
+	(No symbol) [0x0x7ff6f52d0406]
+	(No symbol) [0x0x7ff6f52d06bc]
+	(No symbol) [0x0x7ff6f5323ac7]
+	(No symbol) [0x0x7ff6f52f864f]
+	(No symbol) [0x0x7ff6f532087f]
+	(No symbol) [0x0x7ff6f52f83e3]
+	(No symbol) [0x0x7ff6f52c1521]
+	(No symbol) [0x0x7ff6f52c22b3]
+	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
+	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
+	GetHandleVerifier [0x0x7ff6f54c884e+184862]
+	GetHandleVerifier [0x0x7ff6f54d055f+216879]
+	GetHandleVerifier [0x0x7ff6f54b7084+113236]
+	GetHandleVerifier [0x0x7ff6f54b7239+113673]
+	GetHandleVerifier [0x0x7ff6f549e298+11368]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -3350,25 +3350,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60f7de415+77285]
-	GetHandleVerifier [0x0x7ff60f7de470+77376]
-	(No symbol) [0x0x7ff60f5a9a6a]
-	(No symbol) [0x0x7ff60f600406]
-	(No symbol) [0x0x7ff60f6006bc]
-	(No symbol) [0x0x7ff60f653ac7]
-	(No symbol) [0x0x7ff60f62864f]
-	(No symbol) [0x0x7ff60f65087f]
-	(No symbol) [0x0x7ff60f6283e3]
-	(No symbol) [0x0x7ff60f5f1521]
-	(No symbol) [0x0x7ff60f5f22b3]
-	GetHandleVerifier [0x0x7ff60fac1efd+3107021]
-	GetHandleVerifier [0x0x7ff60fabc29d+3083373]
-	GetHandleVerifier [0x0x7ff60fadbedd+3213485]
-	GetHandleVerifier [0x0x7ff60f7f884e+184862]
-	GetHandleVerifier [0x0x7ff60f80055f+216879]
-	GetHandleVerifier [0x0x7ff60f7e7084+113236]
-	GetHandleVerifier [0x0x7ff60f7e7239+113673]
-	GetHandleVerifier [0x0x7ff60f7ce298+11368]
+	GetHandleVerifier [0x0x7ff6f54ae415+77285]
+	GetHandleVerifier [0x0x7ff6f54ae470+77376]
+	(No symbol) [0x0x7ff6f5279a6a]
+	(No symbol) [0x0x7ff6f52d0406]
+	(No symbol) [0x0x7ff6f52d06bc]
+	(No symbol) [0x0x7ff6f5323ac7]
+	(No symbol) [0x0x7ff6f52f864f]
+	(No symbol) [0x0x7ff6f532087f]
+	(No symbol) [0x0x7ff6f52f83e3]
+	(No symbol) [0x0x7ff6f52c1521]
+	(No symbol) [0x0x7ff6f52c22b3]
+	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
+	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
+	GetHandleVerifier [0x0x7ff6f54c884e+184862]
+	GetHandleVerifier [0x0x7ff6f54d055f+216879]
+	GetHandleVerifier [0x0x7ff6f54b7084+113236]
+	GetHandleVerifier [0x0x7ff6f54b7239+113673]
+	GetHandleVerifier [0x0x7ff6f549e298+11368]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -3471,25 +3471,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff60f7de415+77285]
-	GetHandleVerifier [0x0x7ff60f7de470+77376]
-	(No symbol) [0x0x7ff60f5a9a6a]
-	(No symbol) [0x0x7ff60f600406]
-	(No symbol) [0x0x7ff60f6006bc]
-	(No symbol) [0x0x7ff60f653ac7]
-	(No symbol) [0x0x7ff60f62864f]
-	(No symbol) [0x0x7ff60f65087f]
-	(No symbol) [0x0x7ff60f6283e3]
-	(No symbol) [0x0x7ff60f5f1521]
-	(No symbol) [0x0x7ff60f5f22b3]
-	GetHandleVerifier [0x0x7ff60fac1efd+3107021]
-	GetHandleVerifier [0x0x7ff60fabc29d+3083373]
-	GetHandleVerifier [0x0x7ff60fadbedd+3213485]
-	GetHandleVerifier [0x0x7ff60f7f884e+184862]
-	GetHandleVerifier [0x0x7ff60f80055f+216879]
-	GetHandleVerifier [0x0x7ff60f7e7084+113236]
-	GetHandleVerifier [0x0x7ff60f7e7239+113673]
-	GetHandleVerifier [0x0x7ff60f7ce298+11368]
+	GetHandleVerifier [0x0x7ff6f54ae415+77285]
+	GetHandleVerifier [0x0x7ff6f54ae470+77376]
+	(No symbol) [0x0x7ff6f5279a6a]
+	(No symbol) [0x0x7ff6f52d0406]
+	(No symbol) [0x0x7ff6f52d06bc]
+	(No symbol) [0x0x7ff6f5323ac7]
+	(No symbol) [0x0x7ff6f52f864f]
+	(No symbol) [0x0x7ff6f532087f]
+	(No symbol) [0x0x7ff6f52f83e3]
+	(No symbol) [0x0x7ff6f52c1521]
+	(No symbol) [0x0x7ff6f52c22b3]
+	GetHandleVerifier [0x0x7ff6f5791efd+3107021]
+	GetHandleVerifier [0x0x7ff6f578c29d+3083373]
+	GetHandleVerifier [0x0x7ff6f57abedd+3213485]
+	GetHandleVerifier [0x0x7ff6f54c884e+184862]
+	GetHandleVerifier [0x0x7ff6f54d055f+216879]
+	GetHandleVerifier [0x0x7ff6f54b7084+113236]
+	GetHandleVerifier [0x0x7ff6f54b7239+113673]
+	GetHandleVerifier [0x0x7ff6f549e298+11368]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
